--- a/DataTable/Datas/__enums__.xlsx
+++ b/DataTable/Datas/__enums__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19830" windowHeight="8265"/>
+    <workbookView windowWidth="28800" windowHeight="11220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -86,55 +86,22 @@
     <t>注释</t>
   </si>
   <si>
-    <t>Game.BuffCategoryType</t>
-  </si>
-  <si>
-    <t>Buff类型定义。</t>
-  </si>
-  <si>
-    <t>FireBurn</t>
-  </si>
-  <si>
-    <t>灼烧</t>
-  </si>
-  <si>
-    <t>伤害;间隔帧数</t>
-  </si>
-  <si>
-    <t>Game.SkillCategoryType</t>
-  </si>
-  <si>
-    <t>技能类型定义。</t>
-  </si>
-  <si>
-    <t>FireBall</t>
-  </si>
-  <si>
-    <t>火球</t>
-  </si>
-  <si>
-    <t>Game.ActionCategoryType</t>
-  </si>
-  <si>
-    <t>动作类型定义。</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>造成伤害</t>
-  </si>
-  <si>
-    <t>param_str=伤害表达式</t>
-  </si>
-  <si>
-    <t>AddBuff</t>
-  </si>
-  <si>
-    <t>添加Buff</t>
-  </si>
-  <si>
-    <t>param_list=buffId;层数</t>
+    <t>Demo.DemoType</t>
+  </si>
+  <si>
+    <t>Demo类型定义。</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>一</t>
+  </si>
+  <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>二</t>
   </si>
 </sst>
 </file>
@@ -776,10 +743,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1103,15 +1070,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="23.75" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
     <col min="4" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="9.375" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5083333333333" customWidth="1"/>
+    <col min="8" max="8" width="13.5089285714286" customWidth="1"/>
     <col min="9" max="9" width="8.875" customWidth="1"/>
     <col min="10" max="10" width="12.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.125" customWidth="1"/>
@@ -1139,13 +1106,13 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
+      <c r="I1" s="4"/>
       <c r="J1" s="5"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
@@ -1180,7 +1147,7 @@
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
@@ -1203,7 +1170,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:10">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -1225,71 +1192,16 @@
       <c r="J4" s="1">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
+    </row>
+    <row r="5" spans="8:10">
+      <c r="H5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" t="s">
+      <c r="I5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I9" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="8:11">
-      <c r="H14" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="J5" s="1">
         <v>2</v>
-      </c>
-      <c r="K14" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
